--- a/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
+++ b/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
@@ -1,33 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vijay.kumar\source\repos\SalesForce_Project\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B29B6A5F-2876-4C6C-8086-EE67130B29A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A332BF2-4AEF-486B-9AFD-7FEE9683AB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
     <sheet name="AppName" sheetId="3" r:id="rId2"/>
     <sheet name="ModuleName" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>StdUser</t>
   </si>
@@ -60,6 +71,9 @@
   </si>
   <si>
     <t>Opportunities</t>
+  </si>
+  <si>
+    <t>Project Peloton</t>
   </si>
 </sst>
 </file>
@@ -386,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
@@ -394,7 +408,7 @@
     <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,7 +419,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -413,10 +427,13 @@
         <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>5</v>
       </c>

--- a/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
+++ b/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A332BF2-4AEF-486B-9AFD-7FEE9683AB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB14C32A-29D5-4E16-AF0C-D354D097A64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -401,14 +401,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,7 +420,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -433,7 +434,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>5</v>
       </c>
@@ -447,17 +448,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7496FB9-2313-480C-AF05-5A36CC4344DB}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -470,17 +471,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{895DE476-E756-4B0D-B127-B4197496A436}">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>

--- a/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
+++ b/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB14C32A-29D5-4E16-AF0C-D354D097A64A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10E936A-AD61-41BA-B1CF-2302FCDBB69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>

--- a/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
+++ b/TestData/LV_TC2328_TMTC0002476_VerifyTheRolesAvailableToNonRegisteredUSAndNonUS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D10E936A-AD61-41BA-B1CF-2302FCDBB69B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7983D92E-69D0-407C-A2CA-42051559AD0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6675" yWindow="315" windowWidth="21600" windowHeight="11235" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Users" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>StdUser</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Project Peloton</t>
+  </si>
+  <si>
+    <t>Eli Meyer</t>
+  </si>
+  <si>
+    <t>Ryan Carey</t>
+  </si>
+  <si>
+    <t>In_Active</t>
   </si>
 </sst>
 </file>
@@ -97,12 +106,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -117,9 +132,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -400,16 +416,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -419,13 +436,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -433,9 +453,15 @@
       <c r="D2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
